--- a/VerveStacks_BRA_grids_kan/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids_kan/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93986A91-939D-44AC-B953-13FB372A0621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A368BD7A-E3B5-4AA1-8EE7-61B49203ECD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4F101516-6454-40D0-8E0A-AE9AC0ECEF7A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BED33DDB-0AAB-42E7-9FF7-D56119455BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -78,7 +78,7 @@
     <t>ncap_af~fx</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR141-500__ember</t>
+    <t>ep_bioenergy_BR141-500__irena</t>
   </si>
   <si>
     <t>bioenergy</t>
@@ -93,7 +93,7 @@
     <t>e_BR227-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR227-500__ember</t>
+    <t>ep_bioenergy_BR227-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR292-500</t>
@@ -102,10 +102,10 @@
     <t>e_BR292-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR292-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR300-500__ember</t>
+    <t>ep_bioenergy_BR292-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR300-500__irena</t>
   </si>
   <si>
     <t>e_BR300-500</t>
@@ -117,7 +117,7 @@
     <t>e_BR371-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR371-500__ember</t>
+    <t>ep_bioenergy_BR371-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR373-500</t>
@@ -126,25 +126,25 @@
     <t>e_BR373-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR400-500__ember</t>
+    <t>ep_bioenergy_BR400-500__irena</t>
   </si>
   <si>
     <t>e_BR400-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR446-500__ember</t>
+    <t>ep_bioenergy_BR446-500__irena</t>
   </si>
   <si>
     <t>e_BR446-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR478-500__ember</t>
+    <t>ep_bioenergy_BR478-500__irena</t>
   </si>
   <si>
     <t>e_BR478-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR482-500__ember</t>
+    <t>ep_bioenergy_BR482-500__irena</t>
   </si>
   <si>
     <t>e_BR482-500</t>
@@ -156,10 +156,10 @@
     <t>e_BR487-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR487-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR499-500__ember</t>
+    <t>ep_bioenergy_BR487-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR499-500__irena</t>
   </si>
   <si>
     <t>e_BR499-500</t>
@@ -171,7 +171,7 @@
     <t>e_BR500-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR500-500__ember</t>
+    <t>ep_bioenergy_BR500-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR515-500</t>
@@ -180,7 +180,7 @@
     <t>e_BR515-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR515-500__ember</t>
+    <t>ep_bioenergy_BR515-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR541-500</t>
@@ -189,7 +189,7 @@
     <t>e_BR541-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR541-500__ember</t>
+    <t>ep_bioenergy_BR541-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR543-500</t>
@@ -198,7 +198,7 @@
     <t>e_BR543-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR543-500__ember</t>
+    <t>ep_bioenergy_BR543-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR544-500</t>
@@ -207,7 +207,7 @@
     <t>e_BR544-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR544-500__ember</t>
+    <t>ep_bioenergy_BR544-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR550-500</t>
@@ -216,7 +216,7 @@
     <t>e_BR550-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR550-500__ember</t>
+    <t>ep_bioenergy_BR550-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR556-500</t>
@@ -225,7 +225,7 @@
     <t>e_BR556-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR556-500__ember</t>
+    <t>ep_bioenergy_BR556-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR558-500</t>
@@ -234,7 +234,7 @@
     <t>e_BR558-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR558-500__ember</t>
+    <t>ep_bioenergy_BR558-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR579-500</t>
@@ -243,7 +243,7 @@
     <t>e_BR579-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR579-500__ember</t>
+    <t>ep_bioenergy_BR579-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR580-500</t>
@@ -252,10 +252,10 @@
     <t>e_BR580-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR580-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR592-500__ember</t>
+    <t>ep_bioenergy_BR580-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR592-500__irena</t>
   </si>
   <si>
     <t>e_BR592-500</t>
@@ -267,7 +267,7 @@
     <t>e_BR606-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR606-500__ember</t>
+    <t>ep_bioenergy_BR606-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR609-440</t>
@@ -276,7 +276,7 @@
     <t>e_BR609-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR609-440__ember</t>
+    <t>ep_bioenergy_BR609-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR614-440</t>
@@ -285,10 +285,10 @@
     <t>e_BR614-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR614-440__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR621-440__ember</t>
+    <t>ep_bioenergy_BR614-440__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR621-440__irena</t>
   </si>
   <si>
     <t>e_BR621-440</t>
@@ -300,7 +300,7 @@
     <t>e_BR624-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR624-440__ember</t>
+    <t>ep_bioenergy_BR624-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR625-440</t>
@@ -309,7 +309,7 @@
     <t>e_BR625-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR625-440__ember</t>
+    <t>ep_bioenergy_BR625-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR626-440</t>
@@ -318,7 +318,7 @@
     <t>e_BR626-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR626-440__ember</t>
+    <t>ep_bioenergy_BR626-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR628-440</t>
@@ -327,7 +327,7 @@
     <t>e_BR628-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR628-440__ember</t>
+    <t>ep_bioenergy_BR628-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR629-500</t>
@@ -336,7 +336,7 @@
     <t>e_BR629-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR629-500__ember</t>
+    <t>ep_bioenergy_BR629-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR630-440</t>
@@ -345,7 +345,7 @@
     <t>e_BR630-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR630-440__ember</t>
+    <t>ep_bioenergy_BR630-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR632-440</t>
@@ -354,7 +354,7 @@
     <t>e_BR632-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR632-440__ember</t>
+    <t>ep_bioenergy_BR632-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR639-440</t>
@@ -363,7 +363,7 @@
     <t>e_BR639-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR639-440__ember</t>
+    <t>ep_bioenergy_BR639-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR641-500</t>
@@ -372,10 +372,10 @@
     <t>e_BR641-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR641-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR642-500__ember</t>
+    <t>ep_bioenergy_BR641-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR642-500__irena</t>
   </si>
   <si>
     <t>e_BR642-500</t>
@@ -387,10 +387,10 @@
     <t>e_BR643-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR643-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR646-440__ember</t>
+    <t>ep_bioenergy_BR643-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR646-440__irena</t>
   </si>
   <si>
     <t>e_BR646-440</t>
@@ -402,7 +402,7 @@
     <t>e_BR650-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR650-440__ember</t>
+    <t>ep_bioenergy_BR650-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR657-440</t>
@@ -411,7 +411,7 @@
     <t>e_BR657-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR657-440__ember</t>
+    <t>ep_bioenergy_BR657-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR661-440</t>
@@ -420,7 +420,7 @@
     <t>e_BR661-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR661-440__ember</t>
+    <t>ep_bioenergy_BR661-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR662-440</t>
@@ -429,7 +429,7 @@
     <t>e_BR662-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR662-440__ember</t>
+    <t>ep_bioenergy_BR662-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR663-440</t>
@@ -438,7 +438,7 @@
     <t>e_BR663-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR663-440__ember</t>
+    <t>ep_bioenergy_BR663-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR666-440</t>
@@ -447,10 +447,10 @@
     <t>e_BR666-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR666-440__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR670-440__ember</t>
+    <t>ep_bioenergy_BR666-440__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR670-440__irena</t>
   </si>
   <si>
     <t>e_BR670-440</t>
@@ -462,7 +462,7 @@
     <t>e_BR673-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR673-440__ember</t>
+    <t>ep_bioenergy_BR673-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR676-440</t>
@@ -471,7 +471,7 @@
     <t>e_BR676-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR676-440__ember</t>
+    <t>ep_bioenergy_BR676-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_BR676-500</t>
@@ -480,40 +480,40 @@
     <t>e_BR676-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR676-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR728-440__ember</t>
+    <t>ep_bioenergy_BR676-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR728-440__irena</t>
   </si>
   <si>
     <t>e_BR728-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR732-500__ember</t>
+    <t>ep_bioenergy_BR732-500__irena</t>
   </si>
   <si>
     <t>e_BR732-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR756-440__ember</t>
+    <t>ep_bioenergy_BR756-440__irena</t>
   </si>
   <si>
     <t>e_BR756-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR758-440__ember</t>
+    <t>ep_bioenergy_BR758-440__irena</t>
   </si>
   <si>
     <t>e_BR758-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR777-500__ember</t>
+    <t>ep_bioenergy_BR777-500__irena</t>
   </si>
   <si>
     <t>e_BR777-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR788-500__ember</t>
+    <t>ep_bioenergy_BR788-500__irena</t>
   </si>
   <si>
     <t>e_BR788-500</t>
@@ -525,16 +525,16 @@
     <t>e_BR866-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR866-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_BR903-500__ember</t>
+    <t>ep_bioenergy_BR866-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_BR903-500__irena</t>
   </si>
   <si>
     <t>e_BR903-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_BR984-525__ember</t>
+    <t>ep_bioenergy_BR984-525__irena</t>
   </si>
   <si>
     <t>e_BR984-525</t>
@@ -912,7 +912,7 @@
     <t>ep_bioenergy_r6844204-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_r6844204-500__ember</t>
+    <t>ep_bioenergy_r6844204-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w1090304792-500</t>
@@ -921,7 +921,7 @@
     <t>e_w1090304792-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_w1090304792-500__ember</t>
+    <t>ep_bioenergy_w1090304792-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w160888682-440</t>
@@ -930,7 +930,7 @@
     <t>e_w160888682-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_w167516187-500__ember</t>
+    <t>ep_bioenergy_w167516187-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w168664395-500</t>
@@ -939,16 +939,16 @@
     <t>e_w168664395-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_w168664395-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w172071437-440__ember</t>
+    <t>ep_bioenergy_w168664395-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w172071437-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w174017677-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_w174017677-440__ember</t>
+    <t>ep_bioenergy_w174017677-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w174852067-440</t>
@@ -957,25 +957,25 @@
     <t>e_w174852067-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_w174852067-440__ember</t>
+    <t>ep_bioenergy_w174852067-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w174852067-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_w174852067-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w206109551-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w286006777-440__ember</t>
+    <t>ep_bioenergy_w174852067-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w206109551-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w286006777-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w302735025-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_w302735025-440__ember</t>
+    <t>ep_bioenergy_w302735025-440__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w302735025-500</t>
@@ -984,19 +984,19 @@
     <t>e_w302735025-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_w302735025-500__ember</t>
+    <t>ep_bioenergy_w302735025-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w302931307-440</t>
   </si>
   <si>
-    <t>ep_bioenergy_w302931307-440__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w304646981-500__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w306104018-500__ember</t>
+    <t>ep_bioenergy_w302931307-440__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w304646981-500__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w306104018-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w307168542-230</t>
@@ -1011,13 +1011,13 @@
     <t>e_w348815398-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_w525253078-500__ember</t>
+    <t>ep_bioenergy_w525253078-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w537470701-500</t>
   </si>
   <si>
-    <t>ep_bioenergy_w537470701-500__ember</t>
+    <t>ep_bioenergy_w537470701-500__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w94745966-500</t>
@@ -3012,7 +3012,7 @@
     <t>ele</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR141-500_Missing Bioenergy Capacity -- operating</t>
+    <t>Aggregated Plant - IRENA Gap - BR141-500_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>GW</t>
@@ -3033,58 +3033,58 @@
     <t>Aggregated Plant -- construction</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR487-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR515-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR550-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR579-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR592-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR621-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR626-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR629-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR630-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR632-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR641-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR650-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR657-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR661-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR662-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR663-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR732-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR984-525_Missing Bioenergy Capacity -- operating</t>
+    <t>Aggregated Plant - IRENA Gap - BR487-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR515-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR550-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR579-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR592-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR621-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR626-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR629-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR630-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR632-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR641-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR650-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR657-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR661-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR662-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR663-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR732-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - BR984-525_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>Barra Grande 2 power station_1 -- operating</t>
@@ -3420,16 +3420,16 @@
     <t>Klabin Puma II power station_1 -- operating</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - relation/6844204-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/174017677-440_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/174852067-500_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/537470701-500_Missing Bioenergy Capacity -- operating</t>
+    <t>Aggregated Plant - IRENA Gap - relation/6844204-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/174017677-440_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/174852067-500_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/537470701-500_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>Pampa Sul power station_Unit 1 -- operating</t>
@@ -7175,7 +7175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654010A3-7F97-48BC-8225-0ACAD34A1051}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF05E58-1F11-4AFC-961C-5C8A7BC45650}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7562,7 +7562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{369A0E77-D98D-41EA-9A2E-558858B21BF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FF0753-2BA7-4CA1-9EA0-CDABFA7DDDC3}">
   <dimension ref="B9:T160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16036,7 +16036,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A19147-1498-4CED-8D8F-860187067AB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE15B2F3-896F-4460-8AD9-0D61CE3CE2FB}">
   <dimension ref="B9:T295"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31785,7 +31785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D21A41-9EA1-47BF-914F-2FF8205E6AB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A4EDD5-53F0-4749-83C6-918897846DF1}">
   <dimension ref="B9:T1104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31867,7 +31867,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>6.6080007748934549E-2</v>
+        <v>6.6730071677644331E-2</v>
       </c>
       <c r="G11">
         <v>0.31680000000000003</v>
@@ -31973,7 +31973,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>1.2179452408627152E-2</v>
+        <v>1.2299268113134447E-2</v>
       </c>
       <c r="G13">
         <v>0.30719999999999997</v>
@@ -32132,7 +32132,7 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>4.8458672349218669E-2</v>
+        <v>4.8935385896939181E-2</v>
       </c>
       <c r="G16">
         <v>0.30719999999999997</v>
@@ -32185,7 +32185,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>2.0730982823195149E-2</v>
+        <v>2.0934924447888418E-2</v>
       </c>
       <c r="G17">
         <v>0.30719999999999997</v>
@@ -32344,13 +32344,13 @@
         <v>2022</v>
       </c>
       <c r="F20">
-        <v>1.8657884540875639E-2</v>
+        <v>1.8841432003099578E-2</v>
       </c>
       <c r="G20">
         <v>0.30719999999999997</v>
       </c>
       <c r="H20">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I20">
         <v>152.1</v>
@@ -32450,7 +32450,7 @@
         <v>2022</v>
       </c>
       <c r="F22">
-        <v>2.8245964096603394E-2</v>
+        <v>2.8523834560247971E-2</v>
       </c>
       <c r="G22">
         <v>0.30719999999999997</v>
@@ -32503,7 +32503,7 @@
         <v>2022</v>
       </c>
       <c r="F23">
-        <v>4.9495221490378431E-2</v>
+        <v>4.9982132119333604E-2</v>
       </c>
       <c r="G23">
         <v>0.30719999999999997</v>
@@ -32556,7 +32556,7 @@
         <v>2022</v>
       </c>
       <c r="F24">
-        <v>1.4511687976236606E-2</v>
+        <v>1.4654447113521891E-2</v>
       </c>
       <c r="G24">
         <v>0.30719999999999997</v>
@@ -32565,7 +32565,7 @@
         <v>4016.25</v>
       </c>
       <c r="I24">
-        <v>152.09999999999997</v>
+        <v>152.1</v>
       </c>
       <c r="J24">
         <v>8.64</v>
@@ -32609,13 +32609,13 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>3.4465258943561942E-2</v>
+        <v>3.4804311894614498E-2</v>
       </c>
       <c r="G25">
         <v>0.30719999999999997</v>
       </c>
       <c r="H25">
-        <v>4016.2500000000005</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I25">
         <v>152.1</v>
@@ -32821,19 +32821,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.16066511687976245</v>
+        <v>0.16224566447113525</v>
       </c>
       <c r="G29">
         <v>0.31680000000000003</v>
       </c>
       <c r="H29">
-        <v>3421.2499999999991</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I29">
         <v>128.70000000000002</v>
       </c>
       <c r="J29">
-        <v>7.9200000000000008</v>
+        <v>7.92</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -32874,7 +32874,7 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>3.0319062378922911E-2</v>
+        <v>3.0617327005036814E-2</v>
       </c>
       <c r="G30">
         <v>0.30719999999999997</v>
@@ -32980,7 +32980,7 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>2.2026669249644849E-2</v>
+        <v>2.2243357225881444E-2</v>
       </c>
       <c r="G32">
         <v>0.30719999999999997</v>
@@ -33004,7 +33004,7 @@
         <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q32" t="s">
         <v>991</v>
@@ -33057,7 +33057,7 @@
         <v>47</v>
       </c>
       <c r="P33" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q33" t="s">
         <v>991</v>
@@ -33245,13 +33245,13 @@
         <v>2022</v>
       </c>
       <c r="F37">
-        <v>0.12283107322743128</v>
+        <v>0.12403942735373888</v>
       </c>
       <c r="G37">
         <v>0.31680000000000003</v>
       </c>
       <c r="H37">
-        <v>3421.2499999999991</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I37">
         <v>128.70000000000002</v>
@@ -33404,7 +33404,7 @@
         <v>2022</v>
       </c>
       <c r="F40">
-        <v>4.2757652072839998E-2</v>
+        <v>4.3178281673769858E-2</v>
       </c>
       <c r="G40">
         <v>0.30719999999999997</v>
@@ -33563,13 +33563,13 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>4.2498514787550061E-2</v>
+        <v>4.2916595118171259E-2</v>
       </c>
       <c r="G43">
         <v>0.30719999999999997</v>
       </c>
       <c r="H43">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I43">
         <v>152.1</v>
@@ -33669,7 +33669,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>2.4877179387834184E-2</v>
+        <v>2.5121909337466105E-2</v>
       </c>
       <c r="G45">
         <v>0.30719999999999997</v>
@@ -33828,7 +33828,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.12179452408627152</v>
+        <v>0.12299268113134447</v>
       </c>
       <c r="G48">
         <v>0.31680000000000003</v>
@@ -33934,13 +33934,13 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>1.1920315123337213E-2</v>
+        <v>1.2037581557535841E-2</v>
       </c>
       <c r="G50">
         <v>0.30719999999999997</v>
       </c>
       <c r="H50">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I50">
         <v>152.1</v>
@@ -34040,7 +34040,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>2.5913728528993943E-2</v>
+        <v>2.6168655559860525E-2</v>
       </c>
       <c r="G52">
         <v>0.30719999999999997</v>
@@ -34199,7 +34199,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.11427954281286327</v>
+        <v>0.11540377101898491</v>
       </c>
       <c r="G55">
         <v>0.31680000000000003</v>
@@ -34411,7 +34411,7 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>4.3275926643419879E-2</v>
+        <v>4.370165478496707E-2</v>
       </c>
       <c r="G59">
         <v>0.30719999999999997</v>
@@ -34464,7 +34464,7 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>5.9860712901976004E-2</v>
+        <v>6.0449594343277811E-2</v>
       </c>
       <c r="G60">
         <v>0.31680000000000003</v>
@@ -34623,7 +34623,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>4.9236084205088487E-2</v>
+        <v>4.9720445563734998E-2</v>
       </c>
       <c r="G63">
         <v>0.30719999999999997</v>
@@ -34782,7 +34782,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.6584786258556122E-2</v>
+        <v>1.6747939558310734E-2</v>
       </c>
       <c r="G66">
         <v>0.30719999999999997</v>
@@ -34888,7 +34888,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.2438589693917092E-2</v>
+        <v>1.2560954668733052E-2</v>
       </c>
       <c r="G68">
         <v>0.30719999999999997</v>
@@ -34941,10 +34941,10 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>5.8565026475526305E-2</v>
+        <v>5.9141161565284782E-2</v>
       </c>
       <c r="G69">
-        <v>0.31679999999999997</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="H69">
         <v>3421.2499999999995</v>
@@ -35259,13 +35259,13 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>4.7940397778638788E-2</v>
+        <v>4.8412012785741969E-2</v>
       </c>
       <c r="G75">
         <v>0.30719999999999997</v>
       </c>
       <c r="H75">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I75">
         <v>152.1</v>
@@ -35365,7 +35365,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>2.0730982823195149E-2</v>
+        <v>2.0934924447888418E-2</v>
       </c>
       <c r="G77">
         <v>0.30719999999999997</v>
@@ -35471,7 +35471,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.2249311636316674</v>
+        <v>0.22714393025958934</v>
       </c>
       <c r="G79">
         <v>0.31680000000000003</v>
@@ -35577,7 +35577,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>2.3322355676094548E-2</v>
+        <v>2.355179000387447E-2</v>
       </c>
       <c r="G81">
         <v>0.30719999999999997</v>
@@ -35948,13 +35948,13 @@
         <v>2022</v>
       </c>
       <c r="F88">
-        <v>0.21741618235825916</v>
+        <v>0.2195550201472298</v>
       </c>
       <c r="G88">
         <v>0.31680000000000003</v>
       </c>
       <c r="H88">
-        <v>3421.2499999999991</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I88">
         <v>128.70000000000002</v>
@@ -36107,7 +36107,7 @@
         <v>2022</v>
       </c>
       <c r="F91">
-        <v>8.0850833010461101E-2</v>
+        <v>8.1646205346764839E-2</v>
       </c>
       <c r="G91">
         <v>0.31680000000000003</v>
@@ -36119,7 +36119,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J91">
-        <v>7.9200000000000008</v>
+        <v>7.92</v>
       </c>
       <c r="K91">
         <v>50</v>
@@ -36266,7 +36266,7 @@
         <v>2022</v>
       </c>
       <c r="F94">
-        <v>7.178102802531322E-2</v>
+        <v>7.2487175900813647E-2</v>
       </c>
       <c r="G94">
         <v>0.31680000000000003</v>
@@ -36425,7 +36425,7 @@
         <v>2022</v>
       </c>
       <c r="F97">
-        <v>3.2392160661242425E-2</v>
+        <v>3.2710819449825651E-2</v>
       </c>
       <c r="G97">
         <v>0.30719999999999997</v>
@@ -36584,7 +36584,7 @@
         <v>2022</v>
       </c>
       <c r="F100">
-        <v>7.307671445176292E-2</v>
+        <v>7.3795608678806676E-2</v>
       </c>
       <c r="G100">
         <v>0.31680000000000003</v>
@@ -36596,7 +36596,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J100">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K100">
         <v>50</v>
@@ -36637,13 +36637,13 @@
         <v>2022</v>
       </c>
       <c r="F101">
-        <v>1.8139609970295758E-2</v>
+        <v>1.8318058891902366E-2</v>
       </c>
       <c r="G101">
         <v>0.30719999999999997</v>
       </c>
       <c r="H101">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="I101">
         <v>152.1</v>
@@ -36743,7 +36743,7 @@
         <v>2022</v>
       </c>
       <c r="F103">
-        <v>1.1402040552757333E-2</v>
+        <v>1.1514208446338631E-2</v>
       </c>
       <c r="G103">
         <v>0.30719999999999997</v>
@@ -36796,10 +36796,10 @@
         <v>2022</v>
       </c>
       <c r="F104">
-        <v>1.3734276120366788E-2</v>
+        <v>1.3869387446726077E-2</v>
       </c>
       <c r="G104">
-        <v>0.30719999999999992</v>
+        <v>0.30719999999999997</v>
       </c>
       <c r="H104">
         <v>4016.25</v>
@@ -37008,7 +37008,7 @@
         <v>2022</v>
       </c>
       <c r="F108">
-        <v>7.1521890740023283E-2</v>
+        <v>7.2225489345215041E-2</v>
       </c>
       <c r="G108">
         <v>0.31680000000000003</v>
@@ -37538,7 +37538,7 @@
         <v>2022</v>
       </c>
       <c r="F118">
-        <v>0.32288505747126456</v>
+        <v>0.32606144827586209</v>
       </c>
       <c r="G118">
         <v>0.33599999999999997</v>
@@ -37547,10 +37547,10 @@
         <v>2975</v>
       </c>
       <c r="I118">
-        <v>117</v>
+        <v>116.99999999999999</v>
       </c>
       <c r="J118">
-        <v>7.1999999999999993</v>
+        <v>7.2</v>
       </c>
       <c r="K118">
         <v>50</v>
@@ -37644,7 +37644,7 @@
         <v>2022</v>
       </c>
       <c r="F120">
-        <v>6.2452085754875403E-2</v>
+        <v>6.3066459899263863E-2</v>
       </c>
       <c r="G120">
         <v>0.31680000000000003</v>
@@ -37909,7 +37909,7 @@
         <v>2022</v>
       </c>
       <c r="F125">
-        <v>9.432597184553794E-2</v>
+        <v>9.5253906237892302E-2</v>
       </c>
       <c r="G125">
         <v>0.31680000000000003</v>
@@ -38068,7 +38068,7 @@
         <v>2022</v>
       </c>
       <c r="F128">
-        <v>0.1992765723879634</v>
+        <v>0.20123696125532742</v>
       </c>
       <c r="G128">
         <v>0.31680000000000003</v>
@@ -38174,7 +38174,7 @@
         <v>2022</v>
       </c>
       <c r="F130">
-        <v>2.4099767531964366E-2</v>
+        <v>2.4336849670670287E-2</v>
       </c>
       <c r="G130">
         <v>0.30719999999999997</v>
@@ -38227,7 +38227,7 @@
         <v>2022</v>
       </c>
       <c r="F131">
-        <v>1.9435296396745457E-2</v>
+        <v>1.9626491669895395E-2</v>
       </c>
       <c r="G131">
         <v>0.30719999999999997</v>
@@ -38386,13 +38386,13 @@
         <v>2022</v>
       </c>
       <c r="F134">
-        <v>4.4830750355159515E-2</v>
+        <v>4.5271774118558705E-2</v>
       </c>
       <c r="G134">
         <v>0.30719999999999997</v>
       </c>
       <c r="H134">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="I134">
         <v>152.1</v>
@@ -38492,7 +38492,7 @@
         <v>2022</v>
       </c>
       <c r="F136">
-        <v>2.8245964096603394E-2</v>
+        <v>2.8523834560247971E-2</v>
       </c>
       <c r="G136">
         <v>0.30719999999999997</v>
@@ -38651,7 +38651,7 @@
         <v>2022</v>
       </c>
       <c r="F139">
-        <v>3.5501808084721698E-2</v>
+        <v>3.5851058117008908E-2</v>
       </c>
       <c r="G139">
         <v>0.30719999999999997</v>
@@ -38704,7 +38704,7 @@
         <v>2022</v>
       </c>
       <c r="F140">
-        <v>1.5548237117396365E-2</v>
+        <v>1.5701193335916314E-2</v>
       </c>
       <c r="G140">
         <v>0.30719999999999997</v>
@@ -38713,7 +38713,7 @@
         <v>4016.25</v>
       </c>
       <c r="I140">
-        <v>152.10000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="J140">
         <v>8.64</v>
@@ -38757,7 +38757,7 @@
         <v>2022</v>
       </c>
       <c r="F141">
-        <v>0.15548237117396366</v>
+        <v>0.15701193335916316</v>
       </c>
       <c r="G141">
         <v>0.31680000000000003</v>
@@ -38769,7 +38769,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J141">
-        <v>7.92</v>
+        <v>7.9200000000000017</v>
       </c>
       <c r="K141">
         <v>50</v>
@@ -38810,7 +38810,7 @@
         <v>2022</v>
       </c>
       <c r="F142">
-        <v>2.0730982823195149E-2</v>
+        <v>2.0934924447888418E-2</v>
       </c>
       <c r="G142">
         <v>0.30719999999999997</v>
@@ -38863,7 +38863,7 @@
         <v>2022</v>
       </c>
       <c r="F143">
-        <v>1.2956864264496971E-2</v>
+        <v>1.3084327779930262E-2</v>
       </c>
       <c r="G143">
         <v>0.30719999999999997</v>
@@ -38916,7 +38916,7 @@
         <v>2022</v>
       </c>
       <c r="F144">
-        <v>2.9541650523053093E-2</v>
+        <v>2.9832267338240997E-2</v>
       </c>
       <c r="G144">
         <v>0.30719999999999997</v>
@@ -38969,13 +38969,13 @@
         <v>2022</v>
       </c>
       <c r="F145">
-        <v>2.9282513237763153E-2</v>
+        <v>2.9570580782642391E-2</v>
       </c>
       <c r="G145">
-        <v>0.30720000000000003</v>
+        <v>0.30719999999999997</v>
       </c>
       <c r="H145">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="I145">
         <v>152.1</v>
@@ -39128,13 +39128,13 @@
         <v>2022</v>
       </c>
       <c r="F148">
-        <v>1.8657884540875639E-2</v>
+        <v>1.8841432003099578E-2</v>
       </c>
       <c r="G148">
         <v>0.30719999999999997</v>
       </c>
       <c r="H148">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I148">
         <v>152.1</v>
@@ -39181,7 +39181,7 @@
         <v>2022</v>
       </c>
       <c r="F149">
-        <v>1.2956864264496971E-2</v>
+        <v>1.3084327779930262E-2</v>
       </c>
       <c r="G149">
         <v>0.30719999999999997</v>
@@ -39234,7 +39234,7 @@
         <v>2022</v>
       </c>
       <c r="F150">
-        <v>6.478432132248485E-2</v>
+        <v>6.5421638899651302E-2</v>
       </c>
       <c r="G150">
         <v>0.31680000000000003</v>
@@ -39246,7 +39246,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J150">
-        <v>7.92</v>
+        <v>7.9200000000000017</v>
       </c>
       <c r="K150">
         <v>50</v>
@@ -45382,13 +45382,13 @@
         <v>2022</v>
       </c>
       <c r="F266">
-        <v>0.10624628696887516</v>
+        <v>0.10729148779542814</v>
       </c>
       <c r="G266">
         <v>0.31680000000000003</v>
       </c>
       <c r="H266">
-        <v>3421.25</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I266">
         <v>128.70000000000002</v>
@@ -45594,7 +45594,7 @@
         <v>2022</v>
       </c>
       <c r="F270">
-        <v>2.5913728528993943E-2</v>
+        <v>2.6168655559860525E-2</v>
       </c>
       <c r="G270">
         <v>0.30719999999999997</v>
@@ -45700,7 +45700,7 @@
         <v>2022</v>
       </c>
       <c r="F272">
-        <v>2.0471845537905216E-2</v>
+        <v>2.0673237892289816E-2</v>
       </c>
       <c r="G272">
         <v>0.30719999999999997</v>
@@ -45912,7 +45912,7 @@
         <v>2022</v>
       </c>
       <c r="F276">
-        <v>2.6691140384863758E-2</v>
+        <v>2.6953715226656339E-2</v>
       </c>
       <c r="G276">
         <v>0.30719999999999997</v>
@@ -45921,7 +45921,7 @@
         <v>4016.25</v>
       </c>
       <c r="I276">
-        <v>152.1</v>
+        <v>152.10000000000002</v>
       </c>
       <c r="J276">
         <v>8.64</v>
@@ -45965,7 +45965,7 @@
         <v>2022</v>
       </c>
       <c r="F277">
-        <v>1.2956864264496971E-2</v>
+        <v>1.3084327779930262E-2</v>
       </c>
       <c r="G277">
         <v>0.30719999999999997</v>
@@ -46177,7 +46177,7 @@
         <v>2022</v>
       </c>
       <c r="F281">
-        <v>8.8365814283869332E-2</v>
+        <v>8.9235115459124381E-2</v>
       </c>
       <c r="G281">
         <v>0.31680000000000003</v>
@@ -46389,13 +46389,13 @@
         <v>2022</v>
       </c>
       <c r="F285">
-        <v>3.9648004649360732E-2</v>
+        <v>4.0038043006586602E-2</v>
       </c>
       <c r="G285">
         <v>0.30719999999999997</v>
       </c>
       <c r="H285">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I285">
         <v>152.1</v>
@@ -46601,7 +46601,7 @@
         <v>2022</v>
       </c>
       <c r="F289">
-        <v>7.1003616169443395E-2</v>
+        <v>7.1702116234017815E-2</v>
       </c>
       <c r="G289">
         <v>0.31680000000000003</v>
@@ -46613,7 +46613,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J289">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K289">
         <v>50</v>
@@ -46654,7 +46654,7 @@
         <v>2022</v>
       </c>
       <c r="F290">
-        <v>2.5913728528993943E-2</v>
+        <v>2.6168655559860525E-2</v>
       </c>
       <c r="G290">
         <v>0.30719999999999997</v>
@@ -46707,7 +46707,7 @@
         <v>2022</v>
       </c>
       <c r="F291">
-        <v>1.2956864264496971E-2</v>
+        <v>1.3084327779930262E-2</v>
       </c>
       <c r="G291">
         <v>0.30719999999999997</v>
@@ -46813,7 +46813,7 @@
         <v>2022</v>
       </c>
       <c r="F293">
-        <v>2.2026669249644849E-2</v>
+        <v>2.2243357225881444E-2</v>
       </c>
       <c r="G293">
         <v>0.30719999999999997</v>
@@ -46972,13 +46972,13 @@
         <v>2022</v>
       </c>
       <c r="F296">
-        <v>1.8139609970295758E-2</v>
+        <v>1.8318058891902366E-2</v>
       </c>
       <c r="G296">
         <v>0.30719999999999997</v>
       </c>
       <c r="H296">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="I296">
         <v>152.1</v>
@@ -47078,13 +47078,13 @@
         <v>2022</v>
       </c>
       <c r="F298">
-        <v>3.6279219940591516E-2</v>
+        <v>3.6636117783804732E-2</v>
       </c>
       <c r="G298">
         <v>0.30719999999999997</v>
       </c>
       <c r="H298">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="I298">
         <v>152.1</v>
@@ -47131,7 +47131,7 @@
         <v>2022</v>
       </c>
       <c r="F299">
-        <v>1.4770825261526547E-2</v>
+        <v>1.4916133669120498E-2</v>
       </c>
       <c r="G299">
         <v>0.30719999999999997</v>
@@ -47184,13 +47184,13 @@
         <v>2022</v>
       </c>
       <c r="F300">
-        <v>4.7940397778638788E-2</v>
+        <v>4.8412012785741969E-2</v>
       </c>
       <c r="G300">
         <v>0.30719999999999997</v>
       </c>
       <c r="H300">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="I300">
         <v>152.1</v>
@@ -47343,7 +47343,7 @@
         <v>2022</v>
       </c>
       <c r="F303">
-        <v>1.4252550690946667E-2</v>
+        <v>1.4392760557923288E-2</v>
       </c>
       <c r="G303">
         <v>0.30719999999999997</v>
@@ -47555,7 +47555,7 @@
         <v>2022</v>
       </c>
       <c r="F307">
-        <v>7.851859744285164E-2</v>
+        <v>7.9291026346377386E-2</v>
       </c>
       <c r="G307">
         <v>0.31680000000000003</v>
@@ -47567,7 +47567,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J307">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K307">
         <v>50</v>
@@ -63104,7 +63104,7 @@
         <v>819</v>
       </c>
       <c r="P613" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q613" t="s">
         <v>991</v>
@@ -63157,7 +63157,7 @@
         <v>819</v>
       </c>
       <c r="P614" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q614" t="s">
         <v>991</v>
@@ -63528,7 +63528,7 @@
         <v>829</v>
       </c>
       <c r="P621" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q621" t="s">
         <v>991</v>
@@ -63581,7 +63581,7 @@
         <v>829</v>
       </c>
       <c r="P622" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q622" t="s">
         <v>991</v>
@@ -64111,7 +64111,7 @@
         <v>849</v>
       </c>
       <c r="P632" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q632" t="s">
         <v>991</v>
@@ -64164,7 +64164,7 @@
         <v>849</v>
       </c>
       <c r="P633" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q633" t="s">
         <v>991</v>
@@ -64535,7 +64535,7 @@
         <v>860</v>
       </c>
       <c r="P640" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q640" t="s">
         <v>991</v>
@@ -64588,7 +64588,7 @@
         <v>860</v>
       </c>
       <c r="P641" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q641" t="s">
         <v>991</v>
@@ -64641,7 +64641,7 @@
         <v>862</v>
       </c>
       <c r="P642" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q642" t="s">
         <v>991</v>
@@ -64694,7 +64694,7 @@
         <v>862</v>
       </c>
       <c r="P643" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q643" t="s">
         <v>991</v>
@@ -64944,7 +64944,7 @@
         <v>33</v>
       </c>
       <c r="L648">
-        <v>0.20388199450299424</v>
+        <v>0.20388199450299427</v>
       </c>
       <c r="N648" t="s">
         <v>989</v>
@@ -64991,7 +64991,7 @@
         <v>33</v>
       </c>
       <c r="L649">
-        <v>0.20388199450299424</v>
+        <v>0.20388199450299427</v>
       </c>
       <c r="N649" t="s">
         <v>989</v>
@@ -65038,7 +65038,7 @@
         <v>33</v>
       </c>
       <c r="L650">
-        <v>0.20388199450299424</v>
+        <v>0.20388199450299427</v>
       </c>
       <c r="N650" t="s">
         <v>989</v>
@@ -67343,7 +67343,7 @@
         <v>950</v>
       </c>
       <c r="P691" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q691" t="s">
         <v>991</v>
@@ -67399,7 +67399,7 @@
         <v>950</v>
       </c>
       <c r="P692" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q692" t="s">
         <v>991</v>
@@ -67511,7 +67511,7 @@
         <v>953</v>
       </c>
       <c r="P694" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q694" t="s">
         <v>991</v>
@@ -67567,7 +67567,7 @@
         <v>953</v>
       </c>
       <c r="P695" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q695" t="s">
         <v>991</v>
@@ -67959,7 +67959,7 @@
         <v>964</v>
       </c>
       <c r="P702" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q702" t="s">
         <v>991</v>
@@ -68015,7 +68015,7 @@
         <v>964</v>
       </c>
       <c r="P703" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q703" t="s">
         <v>991</v>
@@ -74176,7 +74176,7 @@
         <v>2025</v>
       </c>
       <c r="F872">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G872">
         <v>1</v>
@@ -74185,7 +74185,7 @@
         <v>1032.75</v>
       </c>
       <c r="I872">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J872">
         <v>0</v>
@@ -74194,7 +74194,7 @@
         <v>30</v>
       </c>
       <c r="L872">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="873" spans="2:12" x14ac:dyDescent="0.45">
@@ -74211,7 +74211,7 @@
         <v>2025</v>
       </c>
       <c r="F873">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G873">
         <v>1</v>
@@ -74220,7 +74220,7 @@
         <v>1032.75</v>
       </c>
       <c r="I873">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J873">
         <v>0</v>
@@ -74229,7 +74229,7 @@
         <v>30</v>
       </c>
       <c r="L873">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="874" spans="2:12" x14ac:dyDescent="0.45">
@@ -78315,7 +78315,7 @@
         <v>33</v>
       </c>
       <c r="L990">
-        <v>0.27725620724980671</v>
+        <v>0.27725620724980676</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.45">
@@ -78341,7 +78341,7 @@
         <v>33</v>
       </c>
       <c r="L991">
-        <v>0.27725620724980671</v>
+        <v>0.27725620724980676</v>
       </c>
     </row>
     <row r="992" spans="2:12" x14ac:dyDescent="0.45">
@@ -78367,7 +78367,7 @@
         <v>33</v>
       </c>
       <c r="L992">
-        <v>0.27725620724980671</v>
+        <v>0.27725620724980676</v>
       </c>
     </row>
     <row r="993" spans="2:12" x14ac:dyDescent="0.45">
@@ -82296,7 +82296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3ECBAA2-CADE-4E4F-88D2-EC7997AEABC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294FCBE9-CBB9-4E2D-B6DA-A084913674BC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
